--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27766-2026 artfynd.xlsx
+++ b/artfynd/A 27766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042884</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136042885</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
